--- a/per-stock/SMR/financials.xlsx
+++ b/per-stock/SMR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3886767872</v>
+        <v>4063281920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2945345024</v>
+        <v>3121858816</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-18.330503</v>
+        <v>-17.519512</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208.19368</v>
+        <v>217.6486</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -717,7 +726,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>yfinance info.freeCashflow (FALLBACK levered estimate — statement TTM unavailable)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11.23</v>
+        <v>11.74</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D37</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C37</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B37</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B35:E35)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1159,7 +1627,9 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
+      <c r="B18" s="3" t="n">
+        <v>163731673</v>
+      </c>
       <c r="C18" s="3" t="n">
         <v>93249872</v>
       </c>
@@ -1169,9 +1639,7 @@
       <c r="E18" s="3" t="n">
         <v>50763844</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>43615304</v>
-      </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1179,7 +1647,9 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="B19" s="3" t="n">
+        <v>163731673</v>
+      </c>
       <c r="C19" s="3" t="n">
         <v>93249872</v>
       </c>
@@ -1189,9 +1659,7 @@
       <c r="E19" s="3" t="n">
         <v>50763844</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>43615304</v>
-      </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1199,7 +1667,9 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
+      <c r="B20" s="3" t="n">
+        <v>-2.17</v>
+      </c>
       <c r="C20" s="3" t="n">
         <v>-1.47</v>
       </c>
@@ -1209,9 +1679,7 @@
       <c r="E20" s="3" t="n">
         <v>-0.51</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-2.349932</v>
-      </c>
+      <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1219,7 +1687,9 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>-2.17</v>
+      </c>
       <c r="C21" s="3" t="n">
         <v>-1.47</v>
       </c>
@@ -1229,9 +1699,7 @@
       <c r="E21" s="3" t="n">
         <v>-0.51</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-2.349932</v>
-      </c>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1754,13 +2222,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1770,6 +2238,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1780,30 +2249,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1828,9 +2302,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-35706300</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1854,6 +2329,7 @@
         <v>0.21</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1862,21 +2338,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-57215000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-81330000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-543908000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-42777000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-35014000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>158598000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1884,18 +2361,19 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
         <v>8878000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>5761000</v>
       </c>
-      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
         <v>-170030000</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>-5183000</v>
       </c>
     </row>
@@ -1905,18 +2383,19 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
         <v>8878000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>5761000</v>
       </c>
-      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
         <v>-170030000</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>-5183000</v>
       </c>
     </row>
@@ -1927,21 +2406,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-50829000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-273319000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-74975000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1950,21 +2430,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>270000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>293000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>305000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>313000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>423000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1973,21 +2454,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>544000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1869000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>5533000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>6273000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>6373000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3057000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1996,21 +2478,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-57215000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-72452000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-538147000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-42777000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-35014000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-11432000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2019,21 +2502,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-57524000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-72722000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-538440000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-43082000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-35327000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-11855000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2041,18 +2525,21 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>10835000</v>
+      </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n">
         <v>5452000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>5211000</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="G12" s="3" t="n">
         <v>3113000</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>2008000</v>
       </c>
     </row>
@@ -2062,18 +2549,21 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>10835000</v>
+      </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
         <v>5452000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>5211000</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>3113000</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>2008000</v>
       </c>
     </row>
@@ -2084,21 +2574,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-59707000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-279080000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>59348700</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2107,21 +2598,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-50829000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-273319000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-74975000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2130,21 +2622,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>58089000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>74530000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>546682000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>51136000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>48702000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>46079000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2153,21 +2646,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-57524000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-72722000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-538440000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-43082000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-35327000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-11855000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2175,18 +2669,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="3" t="n">
+        <v>319712720</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>147685584</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>133417743</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>127718255</v>
       </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n">
         <v>95197500</v>
       </c>
     </row>
@@ -2196,18 +2693,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>319712720</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>147685584</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>133417743</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>127718255</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>95197500</v>
       </c>
     </row>
@@ -2217,18 +2717,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>-1.85</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>-0.18</v>
       </c>
     </row>
@@ -2238,18 +2741,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>-1.85</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-0.18</v>
       </c>
     </row>
@@ -2260,21 +2766,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-50829000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-273319000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-74975000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2283,21 +2790,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-50829000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-273319000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-74975000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2306,21 +2814,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-44015000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-50829000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-273319000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-17641000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-14005000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-74975000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2329,21 +2838,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>2670000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>12983000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>259327000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>19968000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>16390000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>105340000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2352,21 +2862,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-46685000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-63812000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-532646000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-37609000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-30395000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-180315000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2375,21 +2886,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-46685000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-63812000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-532646000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-37609000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-30395000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-180315000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2407,12 +2919,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>342000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1923000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2421,21 +2934,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-46685000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-63812000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-532646000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-37609000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-30053000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-178392000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2444,21 +2958,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>8910000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>5794000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>63000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-169650000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2467,21 +2982,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>32000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>33000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>63000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>380000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2489,18 +3005,19 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
         <v>8878000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>5761000</v>
       </c>
-      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
         <v>-170030000</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>-5183000</v>
       </c>
     </row>
@@ -2510,18 +3027,21 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>10835000</v>
+      </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
         <v>5452000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>5211000</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>3113000</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
         <v>2008000</v>
       </c>
     </row>
@@ -2531,18 +3051,21 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>10835000</v>
+      </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n">
         <v>5452000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>5211000</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="G34" s="3" t="n">
         <v>3113000</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>2008000</v>
       </c>
     </row>
@@ -2553,21 +3076,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-57524000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-72722000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-538440000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-43082000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-35327000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-11855000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2576,21 +3100,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>57545000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>72661000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>541149000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>44863000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>42329000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>43022000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2599,21 +3124,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>19901000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>14300000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>10873000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>10538000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>9934000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>10958000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2622,21 +3148,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>12805000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>13545000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>11054000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>11802000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>9131000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>9370000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2645,21 +3172,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>24839000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>44816000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>519222000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>22523000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>23264000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>22694000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2668,21 +3196,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>24839000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>44816000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>519222000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>22523000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>23264000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>22694000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2691,21 +3220,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>24839000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>44816000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>519222000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>22523000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>23264000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>22694000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2714,21 +3244,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-61000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2709000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>1781000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>7002000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>31167000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2737,21 +3268,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>544000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1869000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>5533000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>6273000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>6373000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>3057000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2760,21 +3292,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>565000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>1808000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>8242000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>8054000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>13375000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>34224000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2783,28 +3316,29 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>565000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1942000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>8210000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>7986000</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>13375000</v>
-      </c>
       <c r="F45" s="3" t="n">
-        <v>34224000</v>
+        <v>13341000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4116,7 +4650,1499 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>323741458</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>318480601</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>167595781</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>133753450</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>133031072</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>323741458</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>318480601</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>167595781</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>133753450</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>133031072</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>728000</v>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1141236000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1143159000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>802982000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>667100000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>678193000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1166874000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1168841000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>828708000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>692871000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>704008000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>877527000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>976516000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>274190000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>337634000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>456157000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1141236000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1143159000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>802982000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>667100000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>678193000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>728000</v>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1166874000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1168841000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>828708000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>692871000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>704008000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1166874000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1168841000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>828708000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>692871000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>704008000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1109897000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1113551000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>434816000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>498862000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>529486000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-56977000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-55290000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-393892000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-194009000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-174522000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1166874000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1168841000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>828708000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>692871000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>704008000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-776886000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-732871000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-682042000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-408723000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-391082000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1943726000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1901678000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1510720000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1101566000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1095062000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>38430000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>298961000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>448319000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>107590000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>88612000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7492000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2905000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2691000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2664000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1356000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7185000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2570000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2209000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2321000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1008000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>58681000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n">
+        <v>23604000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>307000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>335000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>482000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>343000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>348000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>307000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>335000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>482000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>343000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>348000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>30938000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>296056000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>445628000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>104926000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>87256000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>32323000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>32323000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>32327000</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>32327000</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>33064000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1409000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>613000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>299000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>574000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1409000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>613000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>299000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>574000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>728000</v>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>728000</v>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>7243000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>8700000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>6299000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5605000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>21558000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>287163000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>403975000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>66005000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>48750000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>648000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>560000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1376000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1141000</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1356000</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>21558000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>286515000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>403415000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>64629000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>47609000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>21558000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>286515000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>403415000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>64629000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>47609000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1148327000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1412512000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>883135000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>606452000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>618098000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>239862000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>139940000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>163317000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>163892000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>74685000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>27317000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>15613000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>10167000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2769000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1599000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>65092000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>63767000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>63315000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>64338000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>44987000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>118634000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>32954000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>61991000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>69168000</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>25638000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>25682000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>25726000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>25771000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>25815000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>17383000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>17427000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>17471000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>17516000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>17560000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>8255000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>8255000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>8255000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>8255000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>8255000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3181000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2118000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1846000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2284000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-17005000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>-16740000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-18661000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-18411000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-18178000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>20186000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>18664000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>20779000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>20257000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>20462000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>489000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>489000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2189000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2189000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2189000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>331000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>61000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>521000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>176000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>18201000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>16949000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>16904000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>16903000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>16932000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>908465000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1272572000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>719818000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>442560000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>543413000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>4768000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4877000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>7746000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>3918000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>3553000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>10914000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>8468000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8378000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>15187000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>12796000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>13338000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>8468000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8378000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>15187000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>12796000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>13338000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-5488000</v>
+      </c>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>13956000</v>
+      </c>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n">
+        <v>14338000</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>22104000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>890129000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1254217000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>691785000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>420746000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>521422000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>549000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>417800000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>284200000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>123051000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>341129000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>836417000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>407585000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>297695000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>491422000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5356,13 +7382,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5372,6 +7398,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5382,30 +7409,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5418,21 +7450,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-316200000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-204071000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-199940000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-33254000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-22853000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-26461000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5441,21 +7474,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>37261000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>737364000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>462613000</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>99757000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>100806000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5464,15 +7498,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-1522000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-367000</v>
       </c>
-      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n">
         <v>-67000</v>
       </c>
-      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5480,16 +7517,19 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1600000</v>
       </c>
-      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5498,21 +7538,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>346229000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>841517000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>412685000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>302795000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>496522000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>406656000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5521,21 +7562,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>841517000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>412685000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>302795000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>496522000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>406656000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>116728000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5544,21 +7586,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-495288000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>428832000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>109890000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>-193727000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>89866000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>289928000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5567,21 +7610,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>37792000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>737466000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>463802000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>1746000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>102719000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>311389000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5590,21 +7634,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>37792000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>737466000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>463802000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>1746000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>102719000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>311389000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5613,21 +7658,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>531000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>518000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1189000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1746000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>2962000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>213205000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5636,21 +7682,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>37261000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>737364000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>462613000</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>99757000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>100806000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5659,21 +7706,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>37261000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>737364000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>462613000</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>99757000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>100806000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5682,21 +7730,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-218402000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-104930000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-154113000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-162152000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>9933000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>4956000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5705,21 +7754,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-218402000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-104930000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-154113000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-162152000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>9933000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>4956000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5732,7 +7782,8 @@
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5743,21 +7794,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-216880000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-104563000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-153972000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-162219000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>5000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5766,21 +7818,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>228665000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>109327000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>126764000</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>25000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5789,21 +7842,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-445545000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-213890000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-280736000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-162219000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-20000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5812,17 +7866,20 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-1522000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-367000</v>
       </c>
-      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
         <v>-67000</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>151000</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5833,17 +7890,20 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-1522000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-367000</v>
       </c>
-      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n">
         <v>-67000</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>-44000</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5854,21 +7914,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-314678000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-203704000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-199799000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-33321000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-22786000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-26417000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5877,21 +7938,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-314678000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-203704000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-199799000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-33321000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-22786000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-26417000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5900,21 +7962,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-273541000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-144781000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>327752000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-1298000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>2838000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-20904000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5923,21 +7986,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>875000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-8000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>313000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-226000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-74000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>865000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5945,18 +8009,19 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
         <v>-31428000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>99000</v>
       </c>
-      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
         <v>-1147000</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="H26" s="3" t="n">
         <v>1727000</v>
       </c>
     </row>
@@ -5967,21 +8032,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-265232000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-116130000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>340251000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>18208000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-3016000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>7342000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5990,21 +8056,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-1037000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-421000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>2401000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>694000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-1724000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-419000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6013,21 +8080,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-264195000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-115709000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>337850000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>17514000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-1292000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>7761000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6036,21 +8104,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-264195000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-115709000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>337850000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>17514000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-1292000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>7761000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6059,21 +8128,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-7769000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-3573000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-11549000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-371000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-229000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-12061000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6081,14 +8151,15 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
         <v>2721000</v>
       </c>
-      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6097,21 +8168,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-1415000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>3637000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>18565000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-18806000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>6157000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-8886000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6120,21 +8192,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-90000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>3637000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-2394000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>544000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>7766000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-14134000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6146,10 +8219,11 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
         <v>328000</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="H35" s="3" t="n">
         <v>-87000</v>
       </c>
     </row>
@@ -6160,21 +8234,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>5239000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>4665000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>4798000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>5239000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>4458000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>3200000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6186,10 +8261,11 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
         <v>943000</v>
       </c>
-      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6197,9 +8273,7 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
@@ -6212,7 +8286,10 @@
       <c r="F38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6221,21 +8298,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>270000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>293000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>305000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>313000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>423000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6244,21 +8322,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>270000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>293000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>305000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>313000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>423000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6268,11 +8347,9 @@
       </c>
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n">
         <v>45000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>44000</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>44000</v>
@@ -6280,6 +8357,9 @@
       <c r="G41" s="3" t="n">
         <v>44000</v>
       </c>
+      <c r="H41" s="3" t="n">
+        <v>44000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6289,11 +8369,9 @@
       </c>
       <c r="B42" s="3" t="n"/>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n">
         <v>45000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>44000</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>44000</v>
@@ -6301,6 +8379,9 @@
       <c r="G42" s="3" t="n">
         <v>44000</v>
       </c>
+      <c r="H42" s="3" t="n">
+        <v>44000</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6309,21 +8390,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>93000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>382000</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>260000</v>
-      </c>
       <c r="E43" s="3" t="n">
-        <v>269000</v>
+        <v>216000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>379000</v>
+        <v>313000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6332,15 +8414,16 @@
         </is>
       </c>
       <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
         <v>169908000</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>7248000</v>
       </c>
     </row>
@@ -6354,10 +8437,11 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
         <v>170030000</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="H45" s="3" t="n">
         <v>7191000</v>
       </c>
     </row>
@@ -6367,20 +8451,21 @@
           <t>Gain Loss On Sale Of PPE</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
         <v>-46000</v>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>46000</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n">
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n">
         <v>57000</v>
       </c>
     </row>
@@ -6391,34 +8476,35 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-46685000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-63812000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-532646000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-37609000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-30395000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-180315000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6449,6 +8535,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
